--- a/tests/testthat/_output_excel_snaps/xlr_table_to_workbook.xlsx
+++ b/tests/testthat/_output_excel_snaps/xlr_table_to_workbook.xlsx
@@ -172,310 +172,310 @@
   <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="172" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="173" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="174" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="168" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="170" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="171" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="172" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="173" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="174" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="175" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="168" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="170" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="171" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="172" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="173" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="174" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="175" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="182" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="183" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="184" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="185" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="186" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="181" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="182" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="183" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="184" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="185" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="186" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="180" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="181" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="182" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="183" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="184" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="185" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="186" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="187" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="188" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="189" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="190" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="191" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="192" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="193" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="194" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="195" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="196" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="197" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="187" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="188" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="189" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="190" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="191" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="192" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="193" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="194" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="195" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="196" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="197" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="187" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="188" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="189" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="190" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="191" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="192" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="193" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="194" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="195" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="196" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="197" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
